--- a/artfynd/S 450-2026 artfynd.xlsx
+++ b/artfynd/S 450-2026 artfynd.xlsx
@@ -6735,7 +6735,7 @@
         <v>136289084</v>
       </c>
       <c r="B53" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
